--- a/descriptive tables/ratio_income.xlsx
+++ b/descriptive tables/ratio_income.xlsx
@@ -31,25 +31,25 @@
     <t xml:space="preserve">mean_value</t>
   </si>
   <si>
-    <t xml:space="preserve">wage_ratio</t>
+    <t xml:space="preserve">cash_assistance_ratio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">farm_income_ratio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">non_agri_ratio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">other_income_ratio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">remittance_ratio</t>
   </si>
   <si>
     <t xml:space="preserve">rent_ratio</t>
   </si>
   <si>
-    <t xml:space="preserve">remittance_ratio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">farm_income_ratio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cash_assistance_ratio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">other_income_ratio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">non_agri_ratio</t>
+    <t xml:space="preserve">wage_ratio</t>
   </si>
 </sst>
 </file>
@@ -144,6 +144,23 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -329,9 +346,6 @@
   </sheetPr>
   <dimension ref="A1:C50"/>
   <sheetFormatPr defaultColWidth="10.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10.6"/>
-  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
@@ -340,7 +354,7 @@
       <c r="B1" s="0" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="0" t="s">
         <v>2</v>
       </c>
     </row>
@@ -352,84 +366,84 @@
         <v>3</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>0.364946494564548</v>
+        <v>0.0461684218558434</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>0.0150854749086346</v>
+        <v>0.0690684097219339</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>0.177148138311786</v>
+        <v>0.042102943461384</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>0.217312084339436</v>
+        <v>0.0566655976926605</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>0.044197347350661</v>
+        <v>0.043628085509972</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>0.0592290758401796</v>
+        <v>0.0521329528446322</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>0.122081384684756</v>
+        <v>0.0781017110561851</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>0.299024692241853</v>
+        <v>0.216089578930889</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -440,84 +454,84 @@
         <v>4</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>0.00843164900056002</v>
+        <v>0.168028177070761</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>0.26117193491757</v>
+        <v>0.119485673509413</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>0.177153374632961</v>
+        <v>0.145445651374291</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>0.065266929973961</v>
+        <v>0.116513558210372</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>0.0430585642433912</v>
+        <v>0.154519930589363</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>0.145892854989704</v>
+        <v>0.201712024371378</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>0.44888540653764</v>
+        <v>0.134745353222499</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>0.0337667320473472</v>
+        <v>0.113193407445328</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -528,84 +542,84 @@
         <v>5</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>0.1469090826037</v>
+        <v>0.0723001177096645</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>0.159780608041488</v>
+        <v>0.136501477674247</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>0.0508971843527943</v>
+        <v>0.107118717833943</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>0.0592121292269914</v>
+        <v>0.149841924672483</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>0.10054885719004</v>
+        <v>0.118238081548575</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>0.3069031766076</v>
+        <v>0.0511804773214533</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>0.0258203134945261</v>
+        <v>0.0579040747181318</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>0.284845510683372</v>
+        <v>0.0627124567767335</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -616,84 +630,84 @@
         <v>6</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>0.13203654678975</v>
+        <v>0.0670307796628862</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>0.0580309428894436</v>
+        <v>0.0957604143932737</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>0.066763848374036</v>
+        <v>0.0919968894462923</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>0.125599661161272</v>
+        <v>0.0450122424235422</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>0.368708756905248</v>
+        <v>0.176628105966155</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>0.0151709074481437</v>
+        <v>0.265076151133694</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>0.266239990409284</v>
+        <v>0.120803169519887</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>0.0873953122287337</v>
+        <v>0.303214045068482</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -704,84 +718,84 @@
         <v>7</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>0.045910113068684</v>
+        <v>0.267675493608871</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>0.102836818853104</v>
+        <v>0.193040747968934</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>0.113738101086803</v>
+        <v>0.169655128395716</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>0.329126974201951</v>
+        <v>0.0133162273672744</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>0.0213852185886445</v>
+        <v>0.00819429489620998</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>0.213551212747044</v>
+        <v>0.0336968279833488</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>0.149744707711922</v>
+        <v>0.025678822894483</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>0.0479559516319439</v>
+        <v>0.0189663228458957</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -792,84 +806,84 @@
         <v>8</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>0.0883146143742661</v>
+        <v>0.0160305773333287</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>0.149921320744229</v>
+        <v>0.00539325845626067</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="0" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>0.402899765403248</v>
+        <v>0.361871835335887</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B45" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>0.00329284340666107</v>
+        <v>0.318535485013941</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B46" s="0" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>0.184984047760558</v>
+        <v>0.548898811039569</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="0" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B47" s="0" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>0.180059760092423</v>
+        <v>0.265463625632951</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="0" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B48" s="0" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>0.0722114902663104</v>
+        <v>0.350337407597673</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="0" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B49" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>0.0507328715445951</v>
+        <v>0.342436977144968</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -880,7 +894,7 @@
         <v>9</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>0.105819221526204</v>
+        <v>0.381887553748343</v>
       </c>
     </row>
   </sheetData>
